--- a/data/trans_orig/P14B23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2012</t>
+          <t>Población cuya depresión o ansiedad le limita en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>32073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>60343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161312</t>
+          <t>162746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>215002</t>
+          <t>213258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>202262</t>
+          <t>204140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261171</t>
+          <t>264205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>912678</t>
+          <t>913202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>940492</t>
+          <t>941472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1114659</t>
+          <t>1116403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1168349</t>
+          <t>1166915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2042034</t>
+          <t>2039000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2100943</t>
+          <t>2099065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53452</t>
+          <t>53464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70671</t>
+          <t>71253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108166</t>
+          <t>109710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104191</t>
+          <t>105403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150953</t>
+          <t>150257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1909455</t>
+          <t>1909443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1936077</t>
+          <t>1936125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1646426</t>
+          <t>1644882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1683921</t>
+          <t>1683339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3566546</t>
+          <t>3567242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3613308</t>
+          <t>3612096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>22459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471439</t>
+          <t>469661</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>440482</t>
+          <t>441180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454971</t>
+          <t>454895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>917434</t>
+          <t>917354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934232</t>
+          <t>934081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66926</t>
+          <t>67120</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107593</t>
+          <t>106523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253981</t>
+          <t>250917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>323136</t>
+          <t>316222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327757</t>
+          <t>329341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>407477</t>
+          <t>408061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3310040</t>
+          <t>3311110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3350707</t>
+          <t>3350513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3219748</t>
+          <t>3226662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3288903</t>
+          <t>3291967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6553040</t>
+          <t>6552456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6632760</t>
+          <t>6631176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2016</t>
+          <t>Población cuya depresión o ansiedad le limita en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>37364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108910</t>
+          <t>109115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152468</t>
+          <t>153815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133056</t>
+          <t>133136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>183214</t>
+          <t>181930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>718087</t>
+          <t>716983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>737158</t>
+          <t>736550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>842192</t>
+          <t>840845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>885750</t>
+          <t>885545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1565793</t>
+          <t>1567077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1615951</t>
+          <t>1615871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52545</t>
+          <t>52197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79121</t>
+          <t>80699</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120282</t>
+          <t>121135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,47 +2728,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>137396</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>114341</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>161833</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>3,98%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>137396</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>112122</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>162839</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2023840</t>
+          <t>2024188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2049765</t>
+          <t>2050176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1868018</t>
+          <t>1867165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1909179</t>
+          <t>1907601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,47 +2841,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3734</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3927289</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3902852</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3950344</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>96,02%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3734</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3927289</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3901846</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3952563</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,99%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>20210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539012</t>
+          <t>538557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546003</t>
+          <t>546007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532286</t>
+          <t>532532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545177</t>
+          <t>545105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076059</t>
+          <t>1075817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090138</t>
+          <t>1090085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51867</t>
+          <t>51280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84710</t>
+          <t>83160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>206528</t>
+          <t>207700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268610</t>
+          <t>268764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>267417</t>
+          <t>273168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>340988</t>
+          <t>346345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3292908</t>
+          <t>3294458</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3325751</t>
+          <t>3326338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3263490</t>
+          <t>3263336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3325572</t>
+          <t>3324400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6568730</t>
+          <t>6563373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6642301</t>
+          <t>6636550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2023</t>
+          <t>Población cuya depresión o ansiedad le limita en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>30742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54684</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87431</t>
+          <t>87733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116050</t>
+          <t>114850</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>124078</t>
+          <t>123622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161709</t>
+          <t>159145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>460254</t>
+          <t>462287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484412</t>
+          <t>484196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>639458</t>
+          <t>640658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668077</t>
+          <t>667775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1108737</t>
+          <t>1111301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1146368</t>
+          <t>1146824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>43707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86035</t>
+          <t>86655</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99950</t>
+          <t>102799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169830</t>
+          <t>166590</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161817</t>
+          <t>166244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>239666</t>
+          <t>241373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2204292</t>
+          <t>2203672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2246745</t>
+          <t>2246620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2067993</t>
+          <t>2071233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2137873</t>
+          <t>2135024</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4288484</t>
+          <t>4286777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4366333</t>
+          <t>4361906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32599</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37217</t>
+          <t>36706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35099</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62179</t>
+          <t>60410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614024</t>
+          <t>614533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634818</t>
+          <t>635067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>623246</t>
+          <t>623757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641253</t>
+          <t>641512</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1244907</t>
+          <t>1246676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1271987</t>
+          <t>1272124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96838</t>
+          <t>94093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154912</t>
+          <t>150077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>215124</t>
+          <t>219864</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>299743</t>
+          <t>300898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>337457</t>
+          <t>337446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>436691</t>
+          <t>439091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3296977</t>
+          <t>3301812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3355051</t>
+          <t>3357796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3354051</t>
+          <t>3352896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3438670</t>
+          <t>3433930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6668992</t>
+          <t>6666592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6768226</t>
+          <t>6768237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/P14B23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32073</t>
+          <t>32286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60343</t>
+          <t>60127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>162746</t>
+          <t>162159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213258</t>
+          <t>213931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204140</t>
+          <t>204019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>264205</t>
+          <t>261373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>913202</t>
+          <t>913418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>941472</t>
+          <t>941259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1116403</t>
+          <t>1115730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1166915</t>
+          <t>1167502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2039000</t>
+          <t>2041832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2099065</t>
+          <t>2099186</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53464</t>
+          <t>52479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71253</t>
+          <t>70588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109710</t>
+          <t>109797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105403</t>
+          <t>106288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150257</t>
+          <t>153302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1909443</t>
+          <t>1910428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1936125</t>
+          <t>1936629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1644882</t>
+          <t>1644795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1683339</t>
+          <t>1684004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3567242</t>
+          <t>3564197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3612096</t>
+          <t>3611211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17451</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>22383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469661</t>
+          <t>468239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441180</t>
+          <t>441546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454895</t>
+          <t>455036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>917354</t>
+          <t>917430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934081</t>
+          <t>934311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67120</t>
+          <t>67892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106523</t>
+          <t>105304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>250917</t>
+          <t>253762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>316222</t>
+          <t>321395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329341</t>
+          <t>333062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408061</t>
+          <t>405892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3311110</t>
+          <t>3312329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3350513</t>
+          <t>3349741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3226662</t>
+          <t>3221489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3291967</t>
+          <t>3289122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6552456</t>
+          <t>6554625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6631176</t>
+          <t>6627455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109115</t>
+          <t>109427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153815</t>
+          <t>152322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133136</t>
+          <t>132446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181930</t>
+          <t>180695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>716983</t>
+          <t>717812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>736550</t>
+          <t>736696</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>840845</t>
+          <t>842338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>885545</t>
+          <t>885233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1567077</t>
+          <t>1568312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1615871</t>
+          <t>1616561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26209</t>
+          <t>27374</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52197</t>
+          <t>51078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80699</t>
+          <t>80235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121135</t>
+          <t>121096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114341</t>
+          <t>116200</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161833</t>
+          <t>165291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2024188</t>
+          <t>2025307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2050176</t>
+          <t>2049011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1867165</t>
+          <t>1867204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1907601</t>
+          <t>1908065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3902852</t>
+          <t>3899394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3950344</t>
+          <t>3948485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538557</t>
+          <t>538922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546007</t>
+          <t>545998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532532</t>
+          <t>533034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545105</t>
+          <t>545229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075817</t>
+          <t>1075367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090085</t>
+          <t>1089916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>52082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83160</t>
+          <t>84015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>207700</t>
+          <t>207567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268764</t>
+          <t>270538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273168</t>
+          <t>274125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>346345</t>
+          <t>343741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3294458</t>
+          <t>3293603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3326338</t>
+          <t>3325536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3263336</t>
+          <t>3261562</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3324400</t>
+          <t>3324533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6563373</t>
+          <t>6565977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6636550</t>
+          <t>6635593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>42407</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52651</t>
+          <t>54957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100390</t>
+          <t>110466</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87733</t>
+          <t>96893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114850</t>
+          <t>125268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>141167</t>
+          <t>152873</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123622</t>
+          <t>134571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159145</t>
+          <t>173924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>474162</t>
+          <t>536122</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>462287</t>
+          <t>523572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484196</t>
+          <t>546832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>655118</t>
+          <t>711572</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>640658</t>
+          <t>696770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667775</t>
+          <t>725145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1129279</t>
+          <t>1247694</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1111301</t>
+          <t>1226643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1146824</t>
+          <t>1265996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65215</t>
+          <t>70354</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43707</t>
+          <t>55209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86655</t>
+          <t>92563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>141036</t>
+          <t>157492</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102799</t>
+          <t>135786</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166590</t>
+          <t>180078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>206251</t>
+          <t>227846</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166244</t>
+          <t>202567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241373</t>
+          <t>258013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2225112</t>
+          <t>2160212</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2203672</t>
+          <t>2138003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2246620</t>
+          <t>2175357</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2096787</t>
+          <t>2013900</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2071233</t>
+          <t>1991314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2135024</t>
+          <t>2035606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4321899</t>
+          <t>4174113</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4286777</t>
+          <t>4143946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4361906</t>
+          <t>4199392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>30704</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>22638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36706</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34962</t>
+          <t>40351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60410</t>
+          <t>69142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>626812</t>
+          <t>689130</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614533</t>
+          <t>675522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635067</t>
+          <t>698362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>634049</t>
+          <t>704173</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>623757</t>
+          <t>693547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641512</t>
+          <t>712239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1260860</t>
+          <t>1393303</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1246676</t>
+          <t>1377322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1272124</t>
+          <t>1406113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94093</t>
+          <t>113334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150077</t>
+          <t>163434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>267841</t>
+          <t>298662</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>219864</t>
+          <t>271606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>300898</t>
+          <t>328891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>393643</t>
+          <t>433879</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>337446</t>
+          <t>397064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>439091</t>
+          <t>472760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3326087</t>
+          <t>3385465</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3301812</t>
+          <t>3357249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3357796</t>
+          <t>3407349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3385953</t>
+          <t>3429645</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3352896</t>
+          <t>3399416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3433930</t>
+          <t>3456701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6712040</t>
+          <t>6815111</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6666592</t>
+          <t>6776230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6768237</t>
+          <t>6851926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
